--- a/sources/bryan_step4.xlsx
+++ b/sources/bryan_step4.xlsx
@@ -696,6 +696,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
@@ -738,6 +743,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
@@ -778,6 +788,11 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -5591,6 +5606,11 @@
           <t>hmmmhhhhmh</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
@@ -5618,6 +5638,11 @@
           <t>hmmmhhhm</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
@@ -5643,6 +5668,11 @@
       <c r="J110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">

--- a/sources/bryan_step4.xlsx
+++ b/sources/bryan_step4.xlsx
@@ -2799,6 +2799,11 @@
           <t>– &lt;2&lt;1~u</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>&lt;2&lt;1~d</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>– Side Step Lair's Dance</t>
@@ -3723,6 +3728,11 @@
           <t>– u</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>– Side Step Mach</t>
@@ -3946,6 +3956,11 @@
       <c r="A73" t="inlineStr">
         <is>
           <t>– ~f+2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>~b+2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
